--- a/business_forms/047_legal_document_authorization_form--business_forms.xlsx
+++ b/business_forms/047_legal_document_authorization_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option_one</t>
+          <t>option one</t>
         </is>
       </c>
     </row>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option_two</t>
+          <t>option two</t>
         </is>
       </c>
     </row>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option_three</t>
+          <t>option three</t>
         </is>
       </c>
     </row>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option_four</t>
+          <t>option four</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option_five</t>
+          <t>option five</t>
         </is>
       </c>
     </row>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option_nine_one</t>
+          <t>option nine one</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option_nine_two</t>
+          <t>option nine two</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option_ten_one</t>
+          <t>option ten one</t>
         </is>
       </c>
     </row>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option_ten_two</t>
+          <t>option ten two</t>
         </is>
       </c>
     </row>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option_fourteen_one</t>
+          <t>option fourteen one</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option_fourteen_two</t>
+          <t>option fourteen two</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option_fifteen_one</t>
+          <t>option fifteen one</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option_fifteen_two</t>
+          <t>option fifteen two</t>
         </is>
       </c>
     </row>
